--- a/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Forest/Forest_Coded_DataMatrix.xlsx
+++ b/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Forest/Forest_Coded_DataMatrix.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable_Codebook" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data_Matrix'!$A$1:$CD$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data_Matrix'!$A$1:$CI$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD81"/>
+  <dimension ref="A1:CI81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -548,6 +548,11 @@
     <col width="16" customWidth="1" min="80" max="80"/>
     <col width="16" customWidth="1" min="81" max="81"/>
     <col width="16" customWidth="1" min="82" max="82"/>
+    <col width="16" customWidth="1" min="83" max="83"/>
+    <col width="16" customWidth="1" min="84" max="84"/>
+    <col width="16" customWidth="1" min="85" max="85"/>
+    <col width="16" customWidth="1" min="86" max="86"/>
+    <col width="16" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -943,20 +948,45 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>Q77_HealthTools</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Q78_ANMOL_ABHA</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Q79_IHIP_workload</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Q80_ANC_steps</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Q81_Outbreak_report</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
           <t>PU_Mean</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>EE_Mean</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>SI_Mean</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>FC_Internet</t>
         </is>
@@ -984,7 +1014,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1227,16 +1257,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA2" s="2" t="n">
+      <c r="CF2" s="2" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC2" s="2" t="n">
+      <c r="CG2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH2" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD2" s="2" t="n">
+      <c r="CI2" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1262,7 +1292,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1505,16 +1535,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB3" s="3" t="n">
+      <c r="CF3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG3" s="3" t="n">
         <v>2.33</v>
       </c>
-      <c r="CC3" s="3" t="n">
+      <c r="CH3" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD3" s="3" t="n">
+      <c r="CI3" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1540,7 +1570,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -1783,16 +1813,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA4" s="2" t="n">
+      <c r="CF4" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB4" s="2" t="n">
+      <c r="CG4" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC4" s="2" t="n">
+      <c r="CH4" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD4" s="2" t="n">
+      <c r="CI4" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1818,7 +1848,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2061,16 +2091,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA5" s="3" t="n">
+      <c r="CF5" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB5" s="3" t="n">
+      <c r="CG5" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC5" s="3" t="n">
+      <c r="CH5" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD5" s="3" t="n">
+      <c r="CI5" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2096,7 +2126,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -2339,16 +2369,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA6" s="2" t="n">
+      <c r="CF6" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC6" s="2" t="n">
+      <c r="CG6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH6" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD6" s="2" t="n">
+      <c r="CI6" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2374,7 +2404,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2617,16 +2647,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB7" s="3" t="n">
+      <c r="CF7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG7" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC7" s="3" t="n">
+      <c r="CH7" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD7" s="3" t="n">
+      <c r="CI7" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2652,7 +2682,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -2895,16 +2925,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB8" s="2" t="n">
+      <c r="CF8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG8" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC8" s="2" t="n">
+      <c r="CH8" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD8" s="2" t="n">
+      <c r="CI8" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2930,7 +2960,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3173,16 +3203,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB9" s="3" t="n">
+      <c r="CF9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG9" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC9" s="3" t="n">
+      <c r="CH9" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD9" s="3" t="n">
+      <c r="CI9" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3208,7 +3238,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -3451,16 +3481,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC10" s="2" t="n">
+      <c r="CF10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH10" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD10" s="2" t="n">
+      <c r="CI10" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3486,7 +3516,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3729,16 +3759,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD11" s="3" t="n">
+      <c r="CF11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI11" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3764,7 +3794,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -4007,16 +4037,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB12" s="2" t="n">
+      <c r="CF12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG12" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC12" s="2" t="n">
+      <c r="CH12" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD12" s="2" t="n">
+      <c r="CI12" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4042,7 +4072,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -4285,16 +4315,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA13" s="3" t="n">
+      <c r="CF13" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD13" s="3" t="n">
+      <c r="CG13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI13" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4320,7 +4350,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -4563,16 +4593,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA14" s="2" t="n">
+      <c r="CF14" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB14" s="2" t="n">
+      <c r="CG14" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD14" s="2" t="n">
+      <c r="CH14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI14" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4598,7 +4628,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -4841,16 +4871,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA15" s="3" t="n">
+      <c r="CF15" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB15" s="3" t="n">
+      <c r="CG15" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC15" s="3" t="n">
+      <c r="CH15" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD15" s="3" t="n">
+      <c r="CI15" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4876,7 +4906,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -5119,16 +5149,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB16" s="2" t="n">
+      <c r="CF16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG16" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD16" s="2" t="n">
+      <c r="CH16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI16" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5154,7 +5184,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -5397,16 +5427,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA17" s="3" t="n">
+      <c r="CF17" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC17" s="3" t="n">
+      <c r="CG17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH17" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD17" s="3" t="n">
+      <c r="CI17" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5432,7 +5462,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -5675,16 +5705,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD18" s="2" t="n">
+      <c r="CF18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI18" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5710,7 +5740,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -5953,16 +5983,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA19" s="3" t="n">
+      <c r="CF19" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB19" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC19" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD19" s="3" t="n">
+      <c r="CG19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI19" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5988,7 +6018,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -6231,16 +6261,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA20" s="2" t="n">
+      <c r="CF20" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB20" s="2" t="n">
+      <c r="CG20" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC20" s="2" t="n">
+      <c r="CH20" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD20" s="2" t="n">
+      <c r="CI20" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6266,7 +6296,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -6509,16 +6539,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA21" s="3" t="n">
+      <c r="CF21" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB21" s="3" t="n">
+      <c r="CG21" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC21" s="3" t="n">
+      <c r="CH21" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD21" s="3" t="n">
+      <c r="CI21" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6544,7 +6574,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -6787,16 +6817,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA22" s="2" t="n">
+      <c r="CF22" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC22" s="2" t="n">
+      <c r="CG22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH22" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD22" s="2" t="n">
+      <c r="CI22" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6822,7 +6852,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -7065,16 +7095,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA23" s="3" t="n">
+      <c r="CF23" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB23" s="3" t="n">
+      <c r="CG23" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC23" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD23" s="3" t="n">
+      <c r="CH23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI23" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7343,16 +7373,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB24" s="2" t="n">
+      <c r="CF24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG24" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC24" s="2" t="n">
+      <c r="CH24" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD24" s="2" t="n">
+      <c r="CI24" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7378,7 +7408,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -7621,16 +7651,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA25" s="3" t="n">
+      <c r="CF25" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB25" s="3" t="n">
+      <c r="CG25" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC25" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD25" s="3" t="n">
+      <c r="CH25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI25" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7899,16 +7929,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA26" s="2" t="n">
+      <c r="CF26" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CB26" s="2" t="n">
+      <c r="CG26" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC26" s="2" t="n">
+      <c r="CH26" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD26" s="2" t="n">
+      <c r="CI26" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7934,7 +7964,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -8177,16 +8207,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA27" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB27" s="3" t="n">
+      <c r="CF27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG27" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC27" s="3" t="n">
+      <c r="CH27" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD27" s="3" t="n">
+      <c r="CI27" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8212,7 +8242,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -8455,16 +8485,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA28" s="2" t="n">
+      <c r="CF28" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB28" s="2" t="n">
+      <c r="CG28" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC28" s="2" t="n">
+      <c r="CH28" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD28" s="2" t="n">
+      <c r="CI28" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8490,7 +8520,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -8733,16 +8763,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA29" s="3" t="n">
+      <c r="CF29" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB29" s="3" t="n">
+      <c r="CG29" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC29" s="3" t="n">
+      <c r="CH29" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD29" s="3" t="n">
+      <c r="CI29" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8768,7 +8798,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -9011,16 +9041,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA30" s="2" t="n">
+      <c r="CF30" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB30" s="2" t="n">
+      <c r="CG30" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD30" s="2" t="n">
+      <c r="CH30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI30" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9046,7 +9076,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -9289,16 +9319,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA31" s="3" t="n">
+      <c r="CF31" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CB31" s="3" t="n">
+      <c r="CG31" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC31" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD31" s="3" t="n">
+      <c r="CH31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI31" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9324,7 +9354,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -9567,16 +9597,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC32" s="2" t="n">
+      <c r="CF32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH32" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD32" s="2" t="n">
+      <c r="CI32" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9602,7 +9632,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -9845,16 +9875,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB33" s="3" t="n">
+      <c r="CF33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG33" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD33" s="3" t="n">
+      <c r="CH33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI33" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9880,7 +9910,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -10123,16 +10153,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA34" s="2" t="n">
+      <c r="CF34" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB34" s="2" t="n">
+      <c r="CG34" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC34" s="2" t="n">
+      <c r="CH34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD34" s="2" t="n">
+      <c r="CI34" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10158,7 +10188,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -10401,16 +10431,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA35" s="3" t="n">
+      <c r="CF35" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB35" s="3" t="n">
+      <c r="CG35" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC35" s="3" t="n">
+      <c r="CH35" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD35" s="3" t="n">
+      <c r="CI35" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10436,7 +10466,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -10679,16 +10709,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA36" s="2" t="n">
+      <c r="CF36" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB36" s="2" t="n">
+      <c r="CG36" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC36" s="2" t="n">
+      <c r="CH36" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD36" s="2" t="n">
+      <c r="CI36" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10957,16 +10987,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA37" s="3" t="n">
+      <c r="CF37" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB37" s="3" t="n">
+      <c r="CG37" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC37" s="3" t="n">
+      <c r="CH37" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="CD37" s="3" t="n">
+      <c r="CI37" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10992,7 +11022,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -11235,16 +11265,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA38" s="2" t="n">
+      <c r="CF38" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB38" s="2" t="n">
+      <c r="CG38" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC38" s="2" t="n">
+      <c r="CH38" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD38" s="2" t="n">
+      <c r="CI38" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11270,7 +11300,7 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -11513,16 +11543,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA39" s="3" t="n">
+      <c r="CF39" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB39" s="3" t="n">
+      <c r="CG39" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC39" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD39" s="3" t="n">
+      <c r="CH39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI39" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11548,7 +11578,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -11791,16 +11821,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA40" s="2" t="n">
+      <c r="CF40" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB40" s="2" t="n">
+      <c r="CG40" s="2" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC40" s="2" t="n">
+      <c r="CH40" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD40" s="2" t="n">
+      <c r="CI40" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11826,7 +11856,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -12069,16 +12099,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA41" s="3" t="n">
+      <c r="CF41" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB41" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD41" s="3" t="n">
+      <c r="CG41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI41" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12347,16 +12377,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA42" s="2" t="n">
+      <c r="CF42" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB42" s="2" t="n">
+      <c r="CG42" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC42" s="2" t="n">
+      <c r="CH42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD42" s="2" t="n">
+      <c r="CI42" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12382,7 +12412,7 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -12625,16 +12655,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB43" s="3" t="n">
+      <c r="CF43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG43" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD43" s="3" t="n">
+      <c r="CH43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI43" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12660,7 +12690,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -12903,16 +12933,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD44" s="2" t="n">
+      <c r="CF44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI44" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12938,7 +12968,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -13181,16 +13211,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA45" s="3" t="n">
+      <c r="CF45" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB45" s="3" t="n">
+      <c r="CG45" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC45" s="3" t="n">
+      <c r="CH45" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD45" s="3" t="n">
+      <c r="CI45" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13216,7 +13246,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -13459,16 +13489,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA46" s="2" t="n">
+      <c r="CF46" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB46" s="2" t="n">
+      <c r="CG46" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD46" s="2" t="n">
+      <c r="CH46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI46" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13494,7 +13524,7 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -13737,16 +13767,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA47" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB47" s="3" t="n">
+      <c r="CF47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG47" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC47" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD47" s="3" t="n">
+      <c r="CH47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI47" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14015,16 +14045,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA48" s="2" t="n">
+      <c r="CF48" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB48" s="2" t="n">
+      <c r="CG48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CC48" s="2" t="n">
+      <c r="CH48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD48" s="2" t="n">
+      <c r="CI48" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14050,7 +14080,7 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -14293,16 +14323,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB49" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC49" s="3" t="n">
+      <c r="CF49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH49" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD49" s="3" t="n">
+      <c r="CI49" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14328,7 +14358,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -14571,16 +14601,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA50" s="2" t="n">
+      <c r="CF50" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB50" s="2" t="n">
+      <c r="CG50" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD50" s="2" t="n">
+      <c r="CH50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI50" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14606,7 +14636,7 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -14849,16 +14879,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA51" s="3" t="n">
+      <c r="CF51" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB51" s="3" t="n">
+      <c r="CG51" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC51" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD51" s="3" t="n">
+      <c r="CH51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI51" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14884,7 +14914,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -15127,16 +15157,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA52" s="2" t="n">
+      <c r="CF52" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD52" s="2" t="n">
+      <c r="CG52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI52" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15162,7 +15192,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -15405,16 +15435,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA53" s="3" t="n">
+      <c r="CF53" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB53" s="3" t="n">
+      <c r="CG53" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC53" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD53" s="3" t="n">
+      <c r="CH53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI53" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15683,16 +15713,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA54" s="2" t="n">
+      <c r="CF54" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB54" s="2" t="n">
+      <c r="CG54" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD54" s="2" t="n">
+      <c r="CH54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI54" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -15718,7 +15748,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -15961,16 +15991,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA55" s="3" t="n">
+      <c r="CF55" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB55" s="3" t="n">
+      <c r="CG55" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC55" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD55" s="3" t="n">
+      <c r="CH55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI55" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15996,7 +16026,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -16239,16 +16269,16 @@
           <t>Verify on ground and coordinate with range officer</t>
         </is>
       </c>
-      <c r="CA56" s="2" t="n">
+      <c r="CF56" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB56" s="2" t="n">
+      <c r="CG56" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC56" s="2" t="n">
+      <c r="CH56" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD56" s="2" t="n">
+      <c r="CI56" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -16274,7 +16304,7 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -16517,16 +16547,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA57" s="3" t="n">
+      <c r="CF57" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CB57" s="3" t="n">
+      <c r="CG57" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD57" s="3" t="n">
+      <c r="CH57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI57" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16552,7 +16582,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -16795,16 +16825,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB58" s="2" t="n">
+      <c r="CF58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG58" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CD58" s="2" t="n">
+      <c r="CH58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI58" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -16830,7 +16860,7 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -17073,16 +17103,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA59" s="3" t="n">
+      <c r="CF59" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB59" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC59" s="3" t="n">
+      <c r="CG59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH59" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD59" s="3" t="n">
+      <c r="CI59" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -17108,7 +17138,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -17351,16 +17381,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA60" s="2" t="n">
+      <c r="CF60" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC60" s="2" t="n">
+      <c r="CG60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH60" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD60" s="2" t="n">
+      <c r="CI60" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -17386,7 +17416,7 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -17629,16 +17659,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA61" s="3" t="n">
+      <c r="CF61" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB61" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC61" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD61" s="3" t="n">
+      <c r="CG61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI61" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17664,7 +17694,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -17907,16 +17937,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA62" s="2" t="n">
+      <c r="CF62" s="2" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD62" s="2" t="n">
+      <c r="CG62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI62" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17942,7 +17972,7 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -18185,16 +18215,16 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA63" s="3" t="n">
+      <c r="CF63" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="CB63" s="3" t="n">
+      <c r="CG63" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="CC63" s="3" t="n">
+      <c r="CH63" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD63" s="3" t="n">
+      <c r="CI63" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18220,7 +18250,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -18463,16 +18493,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA64" s="2" t="n">
+      <c r="CF64" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB64" s="2" t="n">
+      <c r="CG64" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC64" s="2" t="n">
+      <c r="CH64" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CD64" s="2" t="n">
+      <c r="CI64" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18498,7 +18528,7 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -18741,16 +18771,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA65" s="3" t="n">
+      <c r="CF65" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB65" s="3" t="n">
+      <c r="CG65" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC65" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD65" s="3" t="n">
+      <c r="CH65" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI65" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18776,7 +18806,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -19019,16 +19049,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA66" s="2" t="n">
+      <c r="CF66" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB66" s="2" t="n">
+      <c r="CG66" s="2" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD66" s="2" t="n">
+      <c r="CH66" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI66" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19054,7 +19084,7 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -19297,16 +19327,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA67" s="3" t="n">
+      <c r="CF67" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="CB67" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC67" s="3" t="n">
+      <c r="CG67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH67" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="CD67" s="3" t="n">
+      <c r="CI67" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19332,7 +19362,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -19575,16 +19605,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA68" s="2" t="n">
+      <c r="CF68" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB68" s="2" t="n">
+      <c r="CG68" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC68" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD68" s="2" t="n">
+      <c r="CH68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI68" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19610,7 +19640,7 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -19853,16 +19883,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA69" s="3" t="n">
+      <c r="CF69" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB69" s="3" t="n">
+      <c r="CG69" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="CC69" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD69" s="3" t="n">
+      <c r="CH69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI69" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19888,7 +19918,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -20131,16 +20161,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA70" s="2" t="n">
+      <c r="CF70" s="2" t="n">
         <v>4.25</v>
       </c>
-      <c r="CB70" s="2" t="n">
+      <c r="CG70" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="CC70" s="2" t="n">
+      <c r="CH70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="CD70" s="2" t="n">
+      <c r="CI70" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20409,16 +20439,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA71" s="3" t="n">
+      <c r="CF71" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="CB71" s="3" t="n">
+      <c r="CG71" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="CC71" s="3" t="n">
+      <c r="CH71" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD71" s="3" t="n">
+      <c r="CI71" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -20444,7 +20474,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -20687,16 +20717,16 @@
           <t>Show to senior officer for decision</t>
         </is>
       </c>
-      <c r="CA72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB72" s="2" t="n">
+      <c r="CF72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CG72" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD72" s="2" t="n">
+      <c r="CH72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI72" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -20722,7 +20752,7 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -20965,16 +20995,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA73" s="3" t="n">
+      <c r="CF73" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB73" s="3" t="n">
+      <c r="CG73" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC73" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CD73" s="3" t="n">
+      <c r="CH73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI73" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21000,7 +21030,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -21243,16 +21273,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD74" s="2" t="n">
+      <c r="CF74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI74" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21278,7 +21308,7 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -21521,16 +21551,16 @@
           <t>Check location on map and inform seniors</t>
         </is>
       </c>
-      <c r="CA75" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="CB75" s="3" t="n">
+      <c r="CF75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG75" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC75" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD75" s="3" t="n">
+      <c r="CH75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI75" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21556,7 +21586,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -21799,16 +21829,16 @@
           <t>Report fire location to Ranger</t>
         </is>
       </c>
-      <c r="CA76" s="2" t="n">
+      <c r="CF76" s="2" t="n">
         <v>1.75</v>
       </c>
-      <c r="CB76" s="2" t="n">
+      <c r="CG76" s="2" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC76" s="2" t="n">
+      <c r="CH76" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD76" s="2" t="n">
+      <c r="CI76" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21834,7 +21864,7 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -22077,16 +22107,16 @@
           <t>Report to divisional office and verify with GPS</t>
         </is>
       </c>
-      <c r="CA77" s="3" t="n">
+      <c r="CF77" s="3" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB77" s="3" t="n">
+      <c r="CG77" s="3" t="n">
         <v>3.33</v>
       </c>
-      <c r="CC77" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD77" s="3" t="n">
+      <c r="CH77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI77" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22355,16 +22385,16 @@
           <t>Cross-check with satellite data and dispatch team</t>
         </is>
       </c>
-      <c r="CA78" s="2" t="n">
+      <c r="CF78" s="2" t="n">
         <v>4.75</v>
       </c>
-      <c r="CB78" s="2" t="n">
+      <c r="CG78" s="2" t="n">
         <v>4.67</v>
       </c>
-      <c r="CC78" s="2" t="n">
+      <c r="CH78" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="CD78" s="2" t="n">
+      <c r="CI78" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22390,7 +22420,7 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -22633,16 +22663,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA79" s="3" t="n">
+      <c r="CF79" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="CB79" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CC79" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD79" s="3" t="n">
+      <c r="CG79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CH79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI79" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22668,7 +22698,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -22911,16 +22941,16 @@
           <t>Alert nearest range post and deploy patrol</t>
         </is>
       </c>
-      <c r="CA80" s="2" t="n">
+      <c r="CF80" s="2" t="n">
         <v>3.75</v>
       </c>
-      <c r="CB80" s="2" t="n">
+      <c r="CG80" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="CC80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CD80" s="2" t="n">
+      <c r="CH80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CI80" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -22946,7 +22976,7 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -23189,21 +23219,21 @@
           <t>Forward alert to supervisor on WhatsApp</t>
         </is>
       </c>
-      <c r="CA81" s="3" t="n">
+      <c r="CF81" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="CB81" s="3" t="n">
+      <c r="CG81" s="3" t="n">
         <v>1.67</v>
       </c>
-      <c r="CC81" s="3" t="n">
+      <c r="CH81" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="CD81" s="3" t="n">
+      <c r="CI81" s="3" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CD81"/>
+  <autoFilter ref="A1:CI81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23215,7 +23245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24116,6 +24146,60 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q78_ANMOL_ABHA</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Q78: ANMOL / ABHA usability</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>1-5 Likert (Health)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Q79_IHIP_workload</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Q79: IHIP workload integration</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>1-5 Likert (Health)</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
